--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104595_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104595_W16.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MCKOY</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2629</v>
+        <v>4.0049</v>
       </c>
       <c r="E2" t="n">
-        <v>4.562</v>
+        <v>4.9801</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2991</v>
+        <v>-0.9752999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5419</v>
+        <v>4.4978</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0041</v>
+        <v>-0.9797</v>
       </c>
       <c r="I2" t="n">
-        <v>1.546</v>
+        <v>5.4775</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9003</v>
+        <v>5.268</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1621</v>
+        <v>0.6583</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7382</v>
+        <v>4.6097</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3584</v>
+        <v>-0.7701</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1662</v>
+        <v>-1.638</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8078</v>
+        <v>0.8678</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-4.5526</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8552</v>
+        <v>-1.0298</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4498</v>
+        <v>-0.0931</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5946</v>
+        <v>-0.9367</v>
       </c>
       <c r="V2" t="n">
-        <v>1.639</v>
+        <v>3.2684</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3461</v>
+        <v>4.3579</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>J. MCKOY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4171</v>
+        <v>3.25</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5885</v>
+        <v>3.3242</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1714</v>
+        <v>-0.0742</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4867</v>
+        <v>0.5286</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9856</v>
+        <v>-1.0161</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4724</v>
+        <v>1.5447</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2928</v>
+        <v>0.8554</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6682</v>
+        <v>0.1337</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6246</v>
+        <v>0.7217</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8061</v>
+        <v>-0.3268</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6539</v>
+        <v>-1.1497</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8478</v>
+        <v>0.8229</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.722</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.5367</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6256</v>
+        <v>0.8596</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5383</v>
+        <v>1.2703</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0873</v>
+        <v>-0.4107</v>
       </c>
       <c r="V3" t="n">
-        <v>3.278</v>
+        <v>1.6342</v>
       </c>
       <c r="W3" t="n">
-        <v>4.3707</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5783</v>
+        <v>1.7629</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0392</v>
+        <v>3.4594</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4609</v>
+        <v>-1.6964</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0944</v>
+        <v>-0.2665</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.166</v>
+        <v>-0.7813</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2604</v>
+        <v>0.5148</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0146</v>
+        <v>1.0483</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1487</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8658</v>
+        <v>0.3351</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9202</v>
+        <v>-1.3148</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.3148</v>
+        <v>-1.4945</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3946</v>
+        <v>0.1796</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6427</v>
+        <v>-0.3772</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0907</v>
+        <v>0.2808</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5518999999999999</v>
+        <v>-0.6579</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>3.2684</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.519</v>
+        <v>1.5212</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1617</v>
+        <v>2.423</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6427</v>
+        <v>-0.9018</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2862</v>
+        <v>0.1101</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7821</v>
+        <v>-2.1574</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4959</v>
+        <v>2.2675</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0663</v>
+        <v>2.003</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7304</v>
+        <v>0.1411</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3359</v>
+        <v>1.8618</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3524</v>
+        <v>-1.8929</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5125</v>
+        <v>-2.2986</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1601</v>
+        <v>0.4057</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.607</v>
+        <v>0.5704</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0484</v>
+        <v>0.4899</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5586</v>
+        <v>0.0805</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1853</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>3.278</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2449</v>
+        <v>1.4201</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0889</v>
+        <v>1.3855</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1561</v>
+        <v>0.0346</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7222</v>
+        <v>-0.7126</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.8009</v>
+        <v>-3.7917</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0787</v>
+        <v>3.0791</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0284</v>
+        <v>-0.0543</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.9262</v>
+        <v>-1.938</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8977</v>
+        <v>1.8837</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6938</v>
+        <v>-0.6583</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8747</v>
+        <v>-1.8536</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1809</v>
+        <v>1.1953</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1255</v>
+        <v>0.0433</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0907</v>
+        <v>0.4202</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2163</v>
+        <v>-0.3769</v>
       </c>
       <c r="V6" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="7">
@@ -955,22 +955,22 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -982,13 +982,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.29</v>
+        <v>-0.3728</v>
       </c>
       <c r="E8" t="n">
-        <v>1.559</v>
+        <v>1.546</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8489</v>
+        <v>-1.9188</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1416</v>
+        <v>0.1554</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3276</v>
+        <v>-0.3247</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4692</v>
+        <v>0.4801</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7214</v>
+        <v>1.7155</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L8" t="n">
-        <v>0.821</v>
+        <v>0.8192</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5798</v>
+        <v>-1.5601</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2281</v>
+        <v>-1.221</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4316</v>
+        <v>-0.5283</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.121</v>
+        <v>-0.1209</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3106</v>
+        <v>-0.4074</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5869</v>
+        <v>-0.3907</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.374</v>
+        <v>-0.2547</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2129</v>
+        <v>-0.1361</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3554</v>
+        <v>-0.3571</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6161</v>
+        <v>-1.6142</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2608</v>
+        <v>1.2571</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7899</v>
+        <v>0.7769</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2149</v>
+        <v>-0.2208</v>
       </c>
       <c r="L9" t="n">
-        <v>1.0048</v>
+        <v>0.9977</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1453</v>
+        <v>-1.134</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4012</v>
+        <v>-1.3934</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5511</v>
+        <v>-0.3507</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1905</v>
+        <v>-0.0512</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3605</v>
+        <v>-0.2995</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7556</v>
+        <v>-0.6108</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1143</v>
+        <v>-0.0457</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6412</v>
+        <v>-0.5651</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3387</v>
+        <v>-1.3286</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3334</v>
+        <v>-1.3272</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0053</v>
+        <v>-0.0013</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1639</v>
+        <v>0.1634</v>
       </c>
       <c r="K10" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L10" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5026</v>
+        <v>-1.492</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3853</v>
+        <v>-1.3789</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0974</v>
+        <v>0.0349</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0514</v>
+        <v>0.0185</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.046</v>
+        <v>0.0163</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7561</v>
+        <v>-0.6229</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0136</v>
+        <v>1.1975</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7697</v>
+        <v>-1.8204</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9609</v>
+        <v>0.9648</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3319</v>
+        <v>0.3331</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4241</v>
+        <v>0.4305</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1312,22 +1312,22 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.078</v>
+        <v>0.0466</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0696</v>
+        <v>0.1184</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4568</v>
+        <v>-3.1252</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7121</v>
+        <v>0.2514</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7447</v>
+        <v>-3.3766</v>
       </c>
       <c r="G12" t="n">
-        <v>4.575</v>
+        <v>4.581</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6912</v>
+        <v>0.6867</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8838</v>
+        <v>3.8943</v>
       </c>
       <c r="J12" t="n">
-        <v>6.0337</v>
+        <v>5.9957</v>
       </c>
       <c r="K12" t="n">
-        <v>2.566</v>
+        <v>2.5403</v>
       </c>
       <c r="L12" t="n">
-        <v>3.4678</v>
+        <v>3.4554</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4587</v>
+        <v>-1.4147</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8747</v>
+        <v>-1.8536</v>
       </c>
       <c r="O12" t="n">
-        <v>0.416</v>
+        <v>0.439</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.805</v>
+        <v>-6.8289</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.166</v>
+        <v>-8.194699999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9054</v>
+        <v>-0.5618</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7652</v>
+        <v>0.2715</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1402</v>
+        <v>-0.8333</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.5068</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8656</v>
+        <v>-5.7677</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8708</v>
+        <v>-2.8891</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9948</v>
+        <v>-2.8786</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2526</v>
+        <v>-2.2429</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.2496</v>
+        <v>-3.2457</v>
       </c>
       <c r="I13" t="n">
-        <v>0.997</v>
+        <v>1.0028</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2547</v>
+        <v>-0.2643</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4861</v>
+        <v>-1.4931</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.998</v>
+        <v>-1.9786</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.7635</v>
+        <v>-1.7526</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9324</v>
+        <v>-0.8419</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.121</v>
+        <v>-0.1209</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8115</v>
+        <v>-0.721</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5314999999999994</v>
+        <v>1.226900000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>13.9417</v>
+        <v>15.3776</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.4729</v>
+        <v>-14.1508</v>
       </c>
       <c r="G14" t="n">
-        <v>6.0027</v>
+        <v>6.087899999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.2423</v>
+        <v>-14.2182</v>
       </c>
       <c r="I14" t="n">
-        <v>20.2453</v>
+        <v>20.3062</v>
       </c>
       <c r="J14" t="n">
-        <v>18.2366</v>
+        <v>18.0419</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1375</v>
+        <v>2.017</v>
       </c>
       <c r="L14" t="n">
-        <v>16.0993</v>
+        <v>16.0248</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.2339</v>
+        <v>-11.9539</v>
       </c>
       <c r="N14" t="n">
-        <v>-16.3799</v>
+        <v>-16.2351</v>
       </c>
       <c r="O14" t="n">
-        <v>4.146100000000001</v>
+        <v>4.2811</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.0733</v>
+        <v>-9.1052</v>
       </c>
       <c r="Q14" t="n">
-        <v>-20.4151</v>
+        <v>-20.4868</v>
       </c>
       <c r="R14" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.8561</v>
+        <v>-2.1349</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7258000000000001</v>
+        <v>2.4835</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.5822</v>
+        <v>-4.618499999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>6.3952</v>
+        <v>6.379</v>
       </c>
       <c r="W14" t="n">
-        <v>15.3939</v>
+        <v>15.3389</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.998800000000001</v>
+        <v>-8.959899999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.2485</v>
+        <v>10.1644</v>
       </c>
       <c r="E15" t="n">
-        <v>9.392099999999999</v>
+        <v>9.2111</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.9533</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2234</v>
+        <v>6.1938</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9495</v>
+        <v>4.9405</v>
       </c>
       <c r="I15" t="n">
-        <v>1.274</v>
+        <v>1.2533</v>
       </c>
       <c r="J15" t="n">
-        <v>7.1742</v>
+        <v>7.1222</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7621</v>
+        <v>4.7401</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4121</v>
+        <v>2.3821</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9507</v>
+        <v>-0.9284</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4107</v>
+        <v>0.3575</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6866</v>
+        <v>0.5732</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2758</v>
+        <v>-0.2157</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5597</v>
+        <v>5.0837</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9113</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3516</v>
+        <v>-0.9163</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5749</v>
+        <v>2.567</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3666</v>
+        <v>3.3579</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7917</v>
+        <v>-0.791</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1584</v>
+        <v>2.1349</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8328</v>
+        <v>2.8129</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4165</v>
+        <v>0.432</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5337</v>
+        <v>0.5451</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>1.397</v>
+        <v>0.9233</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4748</v>
+        <v>0.5966</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9221</v>
+        <v>0.3267</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>D. RUSSELL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0934</v>
+        <v>0.9862</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8208</v>
+        <v>1.1207</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2726</v>
+        <v>-0.1345</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0906</v>
+        <v>0.0493</v>
       </c>
       <c r="H17" t="n">
-        <v>0.733</v>
+        <v>2.6223</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6424</v>
+        <v>-2.5731</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8178</v>
+        <v>3.0003</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9697</v>
+        <v>3.0682</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.152</v>
+        <v>-0.0679</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7272</v>
+        <v>-2.951</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2368</v>
+        <v>-0.4458</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4904</v>
+        <v>-2.5052</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>2.7316</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4243</v>
+        <v>0.4817</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2299</v>
+        <v>0.3968</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6542</v>
+        <v>0.0849</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9994</v>
+        <v>0.8424</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.27</v>
+        <v>0.4577</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2693</v>
+        <v>0.3847</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.9587</v>
+        <v>0.0931</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7141999999999999</v>
+        <v>0.7351</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.2444</v>
+        <v>-0.642</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.5411</v>
+        <v>0.8086</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2566</v>
+        <v>0.9653</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.2844</v>
+        <v>-0.1566</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4176</v>
+        <v>-0.7155</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4576</v>
+        <v>-0.2301</v>
       </c>
       <c r="O18" t="n">
-        <v>0.04</v>
+        <v>-0.4854</v>
       </c>
       <c r="P18" t="n">
-        <v>2.722</v>
+        <v>1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>2.722</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1434</v>
+        <v>-0.6864</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1785</v>
+        <v>-0.1233</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0351</v>
+        <v>-0.5631</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0927</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5417</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1981</v>
+        <v>0.419</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3436</v>
+        <v>0.3868</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4032</v>
+        <v>-0.4113</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1113</v>
+        <v>0.1011</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5144</v>
+        <v>-0.5123</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4068</v>
+        <v>0.3912</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3321</v>
+        <v>0.3168</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8099</v>
+        <v>-0.8025</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1893</v>
+        <v>0.079</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2087</v>
+        <v>0.0278</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0194</v>
+        <v>0.0512</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. RUSSELL</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1441</v>
+        <v>0.7565</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3334</v>
+        <v>-1.4119</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4775</v>
+        <v>2.1683</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0631</v>
+        <v>-2.9646</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6248</v>
+        <v>-0.7151</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.5617</v>
+        <v>-2.2495</v>
       </c>
       <c r="J20" t="n">
-        <v>3.0342</v>
+        <v>-2.5637</v>
       </c>
       <c r="K20" t="n">
-        <v>3.0824</v>
+        <v>-0.2693</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0481</v>
+        <v>-2.2945</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.9711</v>
+        <v>-0.4009</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.5135</v>
+        <v>0.0449</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>2.7316</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.0999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4325</v>
+        <v>0.0624</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2284</v>
+        <v>-0.1623</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7376</v>
+        <v>-1.3347</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3521</v>
+        <v>-0.3968</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3855</v>
+        <v>-0.9379</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.255</v>
+        <v>-3.2683</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8687</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.1237</v>
+        <v>-4.1357</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3348</v>
+        <v>-0.3754</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0594</v>
+        <v>1.0407</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3942</v>
+        <v>-1.4161</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9202</v>
+        <v>-2.8929</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.7294</v>
+        <v>-2.7196</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1318</v>
+        <v>1.5466</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1584</v>
+        <v>1.1655</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0266</v>
+        <v>0.3812</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8612</v>
+        <v>-2.2636</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4132</v>
+        <v>-0.2106</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2745</v>
+        <v>-2.053</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4493</v>
+        <v>0.4368</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0939</v>
+        <v>2.0829</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6446</v>
+        <v>-1.6461</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1255</v>
+        <v>1.0942</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0638</v>
+        <v>2.0405</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9383</v>
+        <v>-0.9463</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6762</v>
+        <v>-0.6574</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5819</v>
+        <v>0.1811</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0344</v>
+        <v>0.448</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4525</v>
+        <v>-0.2669</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.5068</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0158</v>
+        <v>-2.9978</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1313</v>
+        <v>0.0008</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1471</v>
+        <v>-2.9987</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8724</v>
+        <v>-1.8624</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4545</v>
+        <v>0.4565</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.3269</v>
+        <v>-2.319</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3814</v>
+        <v>1.3755</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1949</v>
+        <v>1.1893</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.2539</v>
+        <v>-3.238</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.5135</v>
+        <v>-2.5052</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1742</v>
+        <v>0.1833</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3357</v>
+        <v>0.2203</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1615</v>
+        <v>-0.037</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5499</v>
+        <v>-3.9628</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.852</v>
+        <v>-1.2921</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6979</v>
+        <v>-2.6707</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.2883</v>
+        <v>-2.2937</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0548</v>
+        <v>0.0573</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3431</v>
+        <v>-2.351</v>
       </c>
       <c r="J24" t="n">
-        <v>0.867</v>
+        <v>0.8429</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1661</v>
+        <v>0.1584</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7009</v>
+        <v>0.6845</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.1552</v>
+        <v>-3.1365</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.044</v>
+        <v>-3.0355</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1921</v>
+        <v>0.7861</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2238</v>
+        <v>0.369</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4158</v>
+        <v>0.4171</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.6027</v>
+        <v>-6.7748</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3458</v>
+        <v>-0.8367</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.2569</v>
+        <v>-5.9381</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.6266</v>
+        <v>-4.6277</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.3263</v>
+        <v>-4.3399</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.8555</v>
+        <v>-1.8768</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1732</v>
+        <v>0.1724</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.0286</v>
+        <v>-2.0491</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.7711</v>
+        <v>-2.751</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.2976</v>
+        <v>-2.2907</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S25" t="n">
-        <v>1.0997</v>
+        <v>0.9149</v>
       </c>
       <c r="T25" t="n">
-        <v>1.3489</v>
+        <v>0.8823</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2492</v>
+        <v>0.0327</v>
       </c>
       <c r="V25" t="n">
-        <v>-4.21</v>
+        <v>-4.2001</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.3707</v>
+        <v>-4.3579</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5313999999999997</v>
+        <v>1.305400000000003</v>
       </c>
       <c r="E26" t="n">
-        <v>13.3803</v>
+        <v>13.0612</v>
       </c>
       <c r="F26" t="n">
-        <v>-12.8491</v>
+        <v>-11.7561</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.0029</v>
+        <v>-6.087999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>14.2426</v>
+        <v>14.218</v>
       </c>
       <c r="I26" t="n">
-        <v>-20.2452</v>
+        <v>-20.3063</v>
       </c>
       <c r="J26" t="n">
-        <v>12.2339</v>
+        <v>11.9539</v>
       </c>
       <c r="K26" t="n">
-        <v>16.3799</v>
+        <v>16.2353</v>
       </c>
       <c r="L26" t="n">
-        <v>-4.1458</v>
+        <v>-4.2811</v>
       </c>
       <c r="M26" t="n">
-        <v>-18.2366</v>
+        <v>-18.0421</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.1377</v>
+        <v>-2.0171</v>
       </c>
       <c r="O26" t="n">
-        <v>-16.0991</v>
+        <v>-16.025</v>
       </c>
       <c r="P26" t="n">
-        <v>9.073400000000001</v>
+        <v>9.105399999999998</v>
       </c>
       <c r="Q26" t="n">
-        <v>-11.3416</v>
+        <v>-11.3815</v>
       </c>
       <c r="R26" t="n">
-        <v>20.4151</v>
+        <v>20.487</v>
       </c>
       <c r="S26" t="n">
-        <v>3.856399999999999</v>
+        <v>4.6672</v>
       </c>
       <c r="T26" t="n">
-        <v>4.5822</v>
+        <v>4.6186</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.726</v>
+        <v>0.04879999999999995</v>
       </c>
       <c r="V26" t="n">
-        <v>-6.3954</v>
+        <v>-6.379</v>
       </c>
       <c r="W26" t="n">
-        <v>7.906000000000001</v>
+        <v>7.870400000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-14.3014</v>
+        <v>-14.2496</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104595_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104595_W16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.959899999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-4.3579</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104595_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-14.2496</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
